--- a/Data/Data_hand_normalized.xlsx
+++ b/Data/Data_hand_normalized.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lui\Desktop\Göttingen\4. Semester\Reiseberichte Dresden\Deep-Mapping-Dresden\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A39B2B9-F806-4A91-9EF2-03DB9B3721D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AE2EB25-6047-44A1-BE4B-F16C04E52284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="18220" windowHeight="11620" xr2:uid="{41E7A465-A3B3-4A1F-832C-5071955CB22D}"/>
   </bookViews>
@@ -6485,9 +6485,6 @@
     <t>Oberhermsdof</t>
   </si>
   <si>
-    <t>Neustadt</t>
-  </si>
-  <si>
     <t>St. Michael</t>
   </si>
   <si>
@@ -6669,6 +6666,9 @@
   </si>
   <si>
     <t>So wie man nach Rom reiset, um zu lernen, wie man bauen sol; so möchte auch jeder Architekt nicht ohne Nutzen nach Dresden reisen, um an der Kreuzkirche alle mögliche Fehler eines Gebäudes vereinigt zu sehen, und zu lernen, wie man nicht bauen solle.</t>
+  </si>
+  <si>
+    <t>Kathedrale Ss. Trinitatis</t>
   </si>
 </sst>
 </file>
@@ -7194,7 +7194,7 @@
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>2173</v>
+        <v>2172</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -7343,7 +7343,7 @@
         <v>39</v>
       </c>
       <c r="Y2" t="s">
-        <v>2174</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.35">
@@ -7420,7 +7420,7 @@
         <v>39</v>
       </c>
       <c r="Y3" t="s">
-        <v>2175</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.35">
@@ -7502,7 +7502,7 @@
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
       <c r="B5" t="s">
         <v>52</v>
@@ -7805,7 +7805,7 @@
         <v>39</v>
       </c>
       <c r="Y8" t="s">
-        <v>2176</v>
+        <v>2175</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.35">
@@ -8036,7 +8036,7 @@
         <v>39</v>
       </c>
       <c r="Y11" t="s">
-        <v>2177</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.35">
@@ -10962,7 +10962,7 @@
         <v>39</v>
       </c>
       <c r="Y49" t="s">
-        <v>2178</v>
+        <v>2177</v>
       </c>
     </row>
     <row r="50" spans="1:25" x14ac:dyDescent="0.35">
@@ -12271,7 +12271,7 @@
         <v>39</v>
       </c>
       <c r="Y66" t="s">
-        <v>2179</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="67" spans="1:25" x14ac:dyDescent="0.35">
@@ -12738,7 +12738,7 @@
     </row>
     <row r="73" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>2145</v>
+        <v>26</v>
       </c>
       <c r="B73" t="s">
         <v>259</v>
@@ -12969,7 +12969,7 @@
     </row>
     <row r="76" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="B76" t="s">
         <v>268</v>
@@ -13041,7 +13041,7 @@
         <v>39</v>
       </c>
       <c r="Y76" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
     </row>
     <row r="77" spans="1:25" x14ac:dyDescent="0.35">
@@ -13426,7 +13426,7 @@
         <v>39</v>
       </c>
       <c r="Y81" t="s">
-        <v>2181</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="82" spans="1:25" x14ac:dyDescent="0.35">
@@ -13816,7 +13816,7 @@
     </row>
     <row r="87" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>2145</v>
+        <v>26</v>
       </c>
       <c r="B87" t="s">
         <v>259</v>
@@ -14432,7 +14432,7 @@
     </row>
     <row r="95" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
       <c r="B95" t="s">
         <v>315</v>
@@ -15279,7 +15279,7 @@
     </row>
     <row r="106" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
       <c r="B106" t="s">
         <v>344</v>
@@ -19124,7 +19124,7 @@
         <v>39</v>
       </c>
       <c r="Y155" t="s">
-        <v>2182</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="156" spans="1:25" x14ac:dyDescent="0.35">
@@ -19971,7 +19971,7 @@
         <v>39</v>
       </c>
       <c r="Y166" t="s">
-        <v>2183</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="167" spans="1:25" x14ac:dyDescent="0.35">
@@ -21362,7 +21362,7 @@
     </row>
     <row r="185" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>2145</v>
+        <v>26</v>
       </c>
       <c r="B185" t="s">
         <v>259</v>
@@ -21901,7 +21901,7 @@
     </row>
     <row r="192" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>2149</v>
+        <v>2148</v>
       </c>
       <c r="B192" t="s">
         <v>503</v>
@@ -22512,7 +22512,7 @@
         <v>39</v>
       </c>
       <c r="Y199" t="s">
-        <v>2197</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="200" spans="1:25" x14ac:dyDescent="0.35">
@@ -25058,7 +25058,7 @@
     </row>
     <row r="233" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
       <c r="B233" t="s">
         <v>601</v>
@@ -25905,7 +25905,7 @@
     </row>
     <row r="244" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
       <c r="B244" t="s">
         <v>619</v>
@@ -26136,7 +26136,7 @@
     </row>
     <row r="247" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
       <c r="B247" t="s">
         <v>625</v>
@@ -26290,7 +26290,7 @@
     </row>
     <row r="249" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
       <c r="B249" t="s">
         <v>619</v>
@@ -28061,7 +28061,7 @@
     </row>
     <row r="272" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="B272" t="s">
         <v>701</v>
@@ -28133,7 +28133,7 @@
         <v>39</v>
       </c>
       <c r="Y272" t="s">
-        <v>2184</v>
+        <v>2183</v>
       </c>
     </row>
     <row r="273" spans="1:25" x14ac:dyDescent="0.35">
@@ -28287,7 +28287,7 @@
         <v>39</v>
       </c>
       <c r="Y274" t="s">
-        <v>2198</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="275" spans="1:25" x14ac:dyDescent="0.35">
@@ -29365,7 +29365,7 @@
         <v>39</v>
       </c>
       <c r="Y288" t="s">
-        <v>2199</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="289" spans="1:25" x14ac:dyDescent="0.35">
@@ -29519,7 +29519,7 @@
         <v>39</v>
       </c>
       <c r="Y290" t="s">
-        <v>2185</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="291" spans="1:25" x14ac:dyDescent="0.35">
@@ -32835,7 +32835,7 @@
     </row>
     <row r="334" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
       <c r="B334" t="s">
         <v>798</v>
@@ -32907,7 +32907,7 @@
         <v>39</v>
       </c>
       <c r="Y334" t="s">
-        <v>2200</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="335" spans="1:25" x14ac:dyDescent="0.35">
@@ -33061,7 +33061,7 @@
         <v>39</v>
       </c>
       <c r="Y336" t="s">
-        <v>2200</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="337" spans="1:25" x14ac:dyDescent="0.35">
@@ -34370,7 +34370,7 @@
         <v>39</v>
       </c>
       <c r="Y353" t="s">
-        <v>2186</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="354" spans="1:25" x14ac:dyDescent="0.35">
@@ -34447,7 +34447,7 @@
         <v>39</v>
       </c>
       <c r="Y354" t="s">
-        <v>2187</v>
+        <v>2186</v>
       </c>
     </row>
     <row r="355" spans="1:25" x14ac:dyDescent="0.35">
@@ -34914,7 +34914,7 @@
     </row>
     <row r="361" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="B361" t="s">
         <v>858</v>
@@ -35607,7 +35607,7 @@
     </row>
     <row r="370" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>2154</v>
+        <v>2153</v>
       </c>
       <c r="B370" t="s">
         <v>872</v>
@@ -37065,7 +37065,7 @@
         <v>39</v>
       </c>
       <c r="Y388" t="s">
-        <v>2201</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="389" spans="1:25" x14ac:dyDescent="0.35">
@@ -37835,7 +37835,7 @@
         <v>39</v>
       </c>
       <c r="Y398" t="s">
-        <v>2202</v>
+        <v>2201</v>
       </c>
     </row>
     <row r="399" spans="1:25" x14ac:dyDescent="0.35">
@@ -38148,7 +38148,7 @@
     </row>
     <row r="403" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
       <c r="B403" t="s">
         <v>940</v>
@@ -38456,7 +38456,7 @@
     </row>
     <row r="407" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
       <c r="B407" t="s">
         <v>120</v>
@@ -39457,7 +39457,7 @@
     </row>
     <row r="420" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>2155</v>
+        <v>2154</v>
       </c>
       <c r="B420" t="s">
         <v>988</v>
@@ -39760,7 +39760,7 @@
         <v>39</v>
       </c>
       <c r="Y423" t="s">
-        <v>2203</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="424" spans="1:25" x14ac:dyDescent="0.35">
@@ -42306,7 +42306,7 @@
     </row>
     <row r="457" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>2156</v>
+        <v>2155</v>
       </c>
       <c r="B457" t="s">
         <v>1078</v>
@@ -42378,7 +42378,7 @@
         <v>39</v>
       </c>
       <c r="Y457" t="s">
-        <v>2204</v>
+        <v>2203</v>
       </c>
     </row>
     <row r="458" spans="1:25" x14ac:dyDescent="0.35">
@@ -42455,7 +42455,7 @@
         <v>39</v>
       </c>
       <c r="Y458" t="s">
-        <v>2204</v>
+        <v>2203</v>
       </c>
     </row>
     <row r="459" spans="1:25" x14ac:dyDescent="0.35">
@@ -45155,7 +45155,7 @@
     </row>
     <row r="494" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="B494" t="s">
         <v>1138</v>
@@ -45689,7 +45689,7 @@
         <v>39</v>
       </c>
       <c r="Y500" t="s">
-        <v>2196</v>
+        <v>2195</v>
       </c>
     </row>
     <row r="501" spans="1:25" x14ac:dyDescent="0.35">
@@ -45771,7 +45771,7 @@
     </row>
     <row r="502" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
       <c r="B502" t="s">
         <v>1157</v>
@@ -47075,7 +47075,7 @@
         <v>39</v>
       </c>
       <c r="Y518" t="s">
-        <v>2195</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="519" spans="1:25" x14ac:dyDescent="0.35">
@@ -47152,7 +47152,7 @@
         <v>39</v>
       </c>
       <c r="Y519" t="s">
-        <v>2195</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="520" spans="1:25" x14ac:dyDescent="0.35">
@@ -48158,7 +48158,7 @@
     </row>
     <row r="533" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
       <c r="B533" t="s">
         <v>601</v>
@@ -48697,7 +48697,7 @@
     </row>
     <row r="540" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
-        <v>1245</v>
+        <v>2206</v>
       </c>
       <c r="B540" t="s">
         <v>1245</v>
@@ -52157,7 +52157,7 @@
         <v>39</v>
       </c>
       <c r="Y584" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
     </row>
     <row r="585" spans="1:25" x14ac:dyDescent="0.35">
@@ -52234,7 +52234,7 @@
         <v>39</v>
       </c>
       <c r="Y585" t="s">
-        <v>2206</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="586" spans="1:25" x14ac:dyDescent="0.35">
@@ -53086,7 +53086,7 @@
     </row>
     <row r="597" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="B597" t="s">
         <v>1355</v>
@@ -53240,7 +53240,7 @@
     </row>
     <row r="599" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A599" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
       <c r="B599" t="s">
         <v>344</v>
@@ -53856,7 +53856,7 @@
     </row>
     <row r="607" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A607" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
       <c r="B607" t="s">
         <v>26</v>
@@ -54010,7 +54010,7 @@
     </row>
     <row r="609" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A609" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
       <c r="B609" t="s">
         <v>26</v>
@@ -54241,7 +54241,7 @@
     </row>
     <row r="612" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A612" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
       <c r="B612" t="s">
         <v>26</v>
@@ -58707,7 +58707,7 @@
     </row>
     <row r="670" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A670" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
       <c r="B670" t="s">
         <v>344</v>
@@ -59092,7 +59092,7 @@
     </row>
     <row r="675" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A675" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
       <c r="B675" t="s">
         <v>349</v>
@@ -60093,7 +60093,7 @@
     </row>
     <row r="688" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A688" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
       <c r="B688" t="s">
         <v>344</v>
@@ -61094,7 +61094,7 @@
     </row>
     <row r="701" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A701" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="B701" t="s">
         <v>349</v>
@@ -63173,7 +63173,7 @@
     </row>
     <row r="728" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A728" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="B728" t="s">
         <v>880</v>
@@ -63789,7 +63789,7 @@
     </row>
     <row r="736" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A736" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="B736" t="s">
         <v>1355</v>
@@ -64867,7 +64867,7 @@
     </row>
     <row r="750" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A750" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="B750" t="s">
         <v>1355</v>
@@ -65021,7 +65021,7 @@
     </row>
     <row r="752" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A752" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
       <c r="B752" t="s">
         <v>344</v>
@@ -65714,7 +65714,7 @@
     </row>
     <row r="761" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A761" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="B761" t="s">
         <v>1671</v>
@@ -65786,7 +65786,7 @@
         <v>39</v>
       </c>
       <c r="Y761" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="762" spans="1:25" x14ac:dyDescent="0.35">
@@ -68563,7 +68563,7 @@
     </row>
     <row r="798" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A798" t="s">
-        <v>2165</v>
+        <v>2164</v>
       </c>
       <c r="B798" t="s">
         <v>1724</v>
@@ -69020,7 +69020,7 @@
         <v>39</v>
       </c>
       <c r="Y803" t="s">
-        <v>2189</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="804" spans="1:25" x14ac:dyDescent="0.35">
@@ -69097,7 +69097,7 @@
         <v>39</v>
       </c>
       <c r="Y804" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="805" spans="1:25" x14ac:dyDescent="0.35">
@@ -69174,7 +69174,7 @@
         <v>39</v>
       </c>
       <c r="Y805" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
     </row>
     <row r="806" spans="1:25" x14ac:dyDescent="0.35">
@@ -69564,7 +69564,7 @@
     </row>
     <row r="811" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A811" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="B811" t="s">
         <v>1355</v>
@@ -70257,7 +70257,7 @@
     </row>
     <row r="820" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A820" t="s">
-        <v>1245</v>
+        <v>2206</v>
       </c>
       <c r="B820" t="s">
         <v>1758</v>
@@ -73260,7 +73260,7 @@
     </row>
     <row r="859" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A859" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="B859" t="s">
         <v>1355</v>
@@ -75031,7 +75031,7 @@
     </row>
     <row r="882" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A882" t="s">
-        <v>1245</v>
+        <v>2206</v>
       </c>
       <c r="B882" t="s">
         <v>1872</v>
@@ -76725,7 +76725,7 @@
     </row>
     <row r="904" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A904" t="s">
-        <v>1245</v>
+        <v>2206</v>
       </c>
       <c r="B904" t="s">
         <v>1922</v>
@@ -77495,7 +77495,7 @@
     </row>
     <row r="914" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A914" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="B914" t="s">
         <v>1355</v>
@@ -77957,7 +77957,7 @@
     </row>
     <row r="920" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A920" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="B920" t="s">
         <v>1956</v>
@@ -78034,7 +78034,7 @@
     </row>
     <row r="921" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A921" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="B921" t="s">
         <v>1960</v>
@@ -80652,7 +80652,7 @@
     </row>
     <row r="955" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A955" t="s">
-        <v>1245</v>
+        <v>2206</v>
       </c>
       <c r="B955" t="s">
         <v>1245</v>
@@ -80806,7 +80806,7 @@
     </row>
     <row r="957" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A957" t="s">
-        <v>1245</v>
+        <v>2206</v>
       </c>
       <c r="B957" t="s">
         <v>2001</v>
@@ -81345,7 +81345,7 @@
     </row>
     <row r="964" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A964" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
       <c r="B964" t="s">
         <v>2012</v>
@@ -81499,7 +81499,7 @@
     </row>
     <row r="966" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A966" t="s">
-        <v>2168</v>
+        <v>2167</v>
       </c>
       <c r="B966" t="s">
         <v>2018</v>
@@ -82033,7 +82033,7 @@
         <v>39</v>
       </c>
       <c r="Y972" t="s">
-        <v>2192</v>
+        <v>2191</v>
       </c>
     </row>
     <row r="973" spans="1:25" x14ac:dyDescent="0.35">
@@ -82264,7 +82264,7 @@
         <v>39</v>
       </c>
       <c r="Y975" t="s">
-        <v>2193</v>
+        <v>2192</v>
       </c>
     </row>
     <row r="976" spans="1:25" x14ac:dyDescent="0.35">
@@ -82654,7 +82654,7 @@
     </row>
     <row r="981" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A981" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
       <c r="B981" t="s">
         <v>1705</v>
@@ -83578,7 +83578,7 @@
     </row>
     <row r="993" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A993" t="s">
-        <v>2170</v>
+        <v>2169</v>
       </c>
       <c r="B993" t="s">
         <v>2060</v>
@@ -85041,7 +85041,7 @@
     </row>
     <row r="1012" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A1012" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="B1012" t="s">
         <v>1450</v>
@@ -85580,7 +85580,7 @@
     </row>
     <row r="1019" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A1019" t="s">
-        <v>2172</v>
+        <v>2171</v>
       </c>
       <c r="B1019" t="s">
         <v>2117</v>
@@ -85871,7 +85871,7 @@
         <v>39</v>
       </c>
       <c r="Y1022" t="s">
-        <v>2194</v>
+        <v>2193</v>
       </c>
     </row>
   </sheetData>
